--- a/stories/arbres/ATOM-REL.MOQ.003-01.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam rentre du parc avec papa. Le soir, la maison est calme. Adam a les joues chaudes. Il pense à des rires. Des enfants ont ri. Adam a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Papa dit : tu peux raconter. Raconter, c'est dire ce qui s'est passé. Adam dit : on a ri. J'ai ri aussi. Papa écoute. Maman dit : même si on a ri, on raconte. Même si on a ri, papa est là. Adam raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Papa dit : merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Adam boit de l'eau. Il se sent plus léger. La lampe est douce.</t>
+          <t>Adam rentre du parc avec papa. Le soir, la maison est calme. Adam a les joues chaudes. Il pense à des rires. Des enfants ont ri. Adam a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Papa écoute. Même si on a ri, on raconte. Même si on a ri, papa est là. Adam raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Adam boit de l'eau. Il se sent plus léger. La lampe est douce.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rentre du parc avec papa. Le soir, la maison est calme. Adam a les joues chaudes. Il pense à des rires. Des enfants ont ri. Adam a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi.
+papa|Tu peux raconter. Raconter, c'est dire ce qui s'est passé.
+enfant-m|On a ri. J'ai ri aussi. Papa écoute.
+maman|Même si on a ri, on raconte. Même si on a ri, papa est là.
+narrateur|Adam raconte encore un peu. Il parle des rires. Il ne répète pas les mots.
+papa|Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman.
+narrateur|Adam boit de l'eau. Il se sent plus léger. La lampe est douce.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a ri un peu. Que fait-il le soir ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a su raconter. Même si on a ri, il a parlé à papa et maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Adam met son pyjama. Papa lui tient la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-01.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Adam boit de l'eau. Il se sent plus léger. La lampe est douce.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Adam a ri un peu. Que fait-il le soir ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Adam a su raconter. Même si on a ri, il a parlé à papa et maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1849,7 @@
           <t>narrateur|Adam met son pyjama. Papa lui tient la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.003-01.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adam raconte à papa</t>
+          <t>Aniss raconte à papa</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +831,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les chaussures gouttent dans l'entrée. Aniss rentre du parc. Son ventre est serré. Il a ri un peu. Le soir, près de la lampe, il raconte à papa et maman. Même si on a ri, on raconte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam rentre du parc avec papa. Le soir, la maison est calme. Adam a les joues chaudes. Il pense à des rires. Des enfants ont ri. Adam a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Papa écoute. Même si on a ri, on raconte. Même si on a ri, papa est là. Adam raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Adam boit de l'eau. Il se sent plus léger. La lampe est douce.</t>
+          <t>Dans l'entrée, les chaussures gouttent encore. Goutte, goutte, sur le tapis rêche. Une chaussette a glissé, près de la porte. La pluie tapote la vitre. Ça sent la soupe, tout chaud. La lampe du salon a un abat-jour doux. On enlève les chaussures, Aniss. Elles sont lourdes, hein ? Oui, papa. La chaussette, je la prends. Elle est mouillée, elle aussi. Viens près de la lampe. Elle est douce, ce soir. En ce moment, Aniss est à la maison. Il rentre du parc, avec papa. Le soir, la maison est calme. Aniss a les joues chaudes. Il pense à des rires. Des enfants ont ri. Aniss a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Papa écoute. Même si on a ri, on raconte. Même si on a ri, papa t'écoute. Je t'écoute, Aniss. Aniss raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Mon ventre est serré. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Tu as bien fait. Bravo, Aniss. C'est du bon travail. Tu veux un peu d'eau ? Oui, maman. Aniss boit de l'eau. L'eau est fraîche. Il se sent plus léger. La lampe est douce. Tes joues sont moins chaudes, maintenant ? Un peu. On reste encore ici ? Oui. La soupe attend, tout doux. Tu as fini de raconter, pour ce soir ? Oui. J'ai raconté. Même si on a ri. Oui. On raconte, quand même. Le manteau mouillé pend au crochet. Il sent encore le parc. Le radiateur fait tic, tout doux. Je l'entends. La louche attend, près de la soupe. On ira à table, dans un moment. Tu as les pieds au sec, maintenant ? Oui, papa. La pluie tapote encore, plus loin. Les chaussures ne gouttent plus. L'abat-jour fait un rond de lumière.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,20 +1325,77 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Adam rentre du parc avec papa. Le soir, la maison est calme. Adam a les joues chaudes. Il pense à des rires. Des enfants ont ri. Adam a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi.
-papa|Tu peux raconter. Raconter, c'est dire ce qui s'est passé.
-enfant-m|On a ri. J'ai ri aussi. Papa écoute.
-maman|Même si on a ri, on raconte. Même si on a ri, papa est là.
-narrateur|Adam raconte encore un peu. Il parle des rires. Il ne répète pas les mots.
-papa|Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman.
-narrateur|Adam boit de l'eau. Il se sent plus léger. La lampe est douce.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>enfants_parc</t>
-        </is>
-      </c>
+          <t>narrateur|Dans l'entrée, les chaussures gouttent encore.
+narrateur|Goutte, goutte, sur le tapis rêche.
+narrateur|Une chaussette a glissé, près de la porte.
+narrateur|La pluie tapote la vitre.
+narrateur|Ça sent la soupe, tout chaud.
+narrateur|La lampe du salon a un abat-jour doux.
+papa|On enlève les chaussures, Aniss.
+papa|Elles sont lourdes, hein ?
+enfant-m|Oui, papa.
+maman|La chaussette, je la prends.
+maman|Elle est mouillée, elle aussi.
+papa|Viens près de la lampe.
+papa|Elle est douce, ce soir.
+narrateur|En ce moment, Aniss est à la maison.
+narrateur|Il rentre du parc, avec papa.
+narrateur|Le soir, la maison est calme.
+narrateur|Aniss a les joues chaudes.
+narrateur|Il pense à des rires.
+narrateur|Des enfants ont ri.
+narrateur|Aniss a ri un peu aussi.
+narrateur|Son ventre est serré.
+narrateur|Maman s'assoit près de lui.
+narrateur|Papa s'assoit aussi.
+papa|Tu peux raconter.
+papa|Raconter, c'est dire ce qui s'est passé.
+enfant-m|On a ri.
+enfant-m|J'ai ri aussi.
+narrateur|Papa écoute.
+maman|Même si on a ri, on raconte.
+maman|Même si on a ri, papa t'écoute.
+papa|Je t'écoute, Aniss.
+narrateur|Aniss raconte encore un peu.
+narrateur|Il parle des rires.
+narrateur|Il ne répète pas les mots.
+enfant-m|Mon ventre est serré.
+papa|Merci d'avoir raconté.
+papa|Même si on a ri, on raconte à papa ou maman.
+maman|Tu as bien fait.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+maman|Tu veux un peu d'eau ?
+enfant-m|Oui, maman.
+narrateur|Aniss boit de l'eau.
+narrateur|L'eau est fraîche.
+narrateur|Il se sent plus léger.
+narrateur|La lampe est douce.
+papa|Tes joues sont moins chaudes, maintenant ?
+enfant-m|Un peu.
+papa|On reste encore ici ?
+enfant-m|Oui.
+maman|La soupe attend, tout doux.
+maman|Tu as fini de raconter, pour ce soir ?
+enfant-m|Oui.
+enfant-m|J'ai raconté.
+papa|Même si on a ri.
+maman|Oui.
+maman|On raconte, quand même.
+narrateur|Le manteau mouillé pend au crochet.
+narrateur|Il sent encore le parc.
+papa|Le radiateur fait tic, tout doux.
+enfant-m|Je l'entends.
+maman|La louche attend, près de la soupe.
+maman|On ira à table, dans un moment.
+papa|Tu as les pieds au sec, maintenant ?
+enfant-m|Oui, papa.
+narrateur|La pluie tapote encore, plus loin.
+narrateur|Les chaussures ne gouttent plus.
+narrateur|L'abat-jour fait un rond de lumière.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1350,7 +1420,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Adam a ri un peu. Que fait-il le soir ?</t>
+          <t>Aniss a ri un peu. Que fait-il le soir ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1576,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Adam a ri un peu. Que fait-il le soir ?</t>
+          <t>narrateur|Aniss a ri un peu.
+narrateur|Que fait-il le soir ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1605,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam a su raconter. Même si on a ri, il a parlé à papa et maman.</t>
+          <t>Aniss a su raconter. Même si on a ri, il a parlé à papa et maman. Bravo, Aniss. Tu as fait du bon travail. Tu es venu nous le dire. J'ai raconté. Oui. Même si on a ri.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1749,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Adam a su raconter. Même si on a ri, il a parlé à papa et maman.</t>
+          <t>narrateur|Aniss a su raconter.
+narrateur|Même si on a ri, il a parlé à papa et maman.
+papa|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+maman|Tu es venu nous le dire.
+enfant-m|J'ai raconté.
+papa|Oui.
+maman|Même si on a ri.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Adam met son pyjama. Papa lui tient la main.</t>
+          <t>Aniss met son pyjama. Le tissu est doux, hein ? Oui, papa. Papa lui tient la main. La lampe reste allumée, un peu. Tu as le ventre plus calme ? Oui. La soupe n'est plus trop chaude. La chaussette sèche, près de la porte.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1924,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Adam met son pyjama. Papa lui tient la main.</t>
+          <t>narrateur|Aniss met son pyjama.
+papa|Le tissu est doux, hein ?
+enfant-m|Oui, papa.
+narrateur|Papa lui tient la main.
+maman|La lampe reste allumée, un peu.
+papa|Tu as le ventre plus calme ?
+enfant-m|Oui.
+maman|La soupe n'est plus trop chaude.
+narrateur|La chaussette sèche, près de la porte.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1874,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté. Même si j'ai ri. Bravo. Tu as fait du bon travail. La lampe est encore douce. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,7 +2100,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai raconté.
+enfant-m|Même si j'ai ri.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|La lampe est encore douce.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2036,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-01.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-01.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dans l'entrée, les chaussures gouttent encore. Goutte, goutte, sur le tapis rêche. Une chaussette a glissé, près de la porte. La pluie tapote la vitre. Ça sent la soupe, tout chaud. La lampe du salon a un abat-jour doux. On enlève les chaussures, Aniss. Elles sont lourdes, hein ? Oui, papa. La chaussette, je la prends. Elle est mouillée, elle aussi. Viens près de la lampe. Elle est douce, ce soir. En ce moment, Aniss est à la maison. Il rentre du parc, avec papa. Le soir, la maison est calme. Aniss a les joues chaudes. Il pense à des rires. Des enfants ont ri. Aniss a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Papa écoute. Même si on a ri, on raconte. Même si on a ri, papa t'écoute. Je t'écoute, Aniss. Aniss raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Mon ventre est serré. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Tu as bien fait. Bravo, Aniss. C'est du bon travail. Tu veux un peu d'eau ? Oui, maman. Aniss boit de l'eau. L'eau est fraîche. Il se sent plus léger. La lampe est douce. Tes joues sont moins chaudes, maintenant ? Un peu. On reste encore ici ? Oui. La soupe attend, tout doux. Tu as fini de raconter, pour ce soir ? Oui. J'ai raconté. Même si on a ri. Oui. On raconte, quand même. Le manteau mouillé pend au crochet. Il sent encore le parc. Le radiateur fait tic, tout doux. Je l'entends. La louche attend, près de la soupe. On ira à table, dans un moment. Tu as les pieds au sec, maintenant ? Oui, papa. La pluie tapote encore, plus loin. Les chaussures ne gouttent plus. L'abat-jour fait un rond de lumière.</t>
+          <t>Dans l'entrée, les chaussures gouttent encore. Goutte, goutte, sur le tapis rêche. Une chaussette a glissé, près de la porte. La pluie tapote la vitre. Ça sent la soupe, tout chaud. La lampe du salon a un abat-jour doux. On enlève les chaussures, Aniss. Elles sont lourdes, hein ? Oui, papa. La chaussette, je la prends. Elle est mouillée, elle aussi. Viens près de la lampe. Elle est douce, ce soir. En ce moment, Aniss est à la maison. Il rentre du parc, avec papa. Le soir, la maison est calme. Aniss a les joues chaudes. Il pense à des rires. Des enfants ont ri. Aniss a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Papa écoute. Même si on a ri, on raconte. Même si on a ri, papa t'écoute. Je t'écoute, Aniss. Aniss raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Mon ventre est serré. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Tu as bien fait. Bravo, Aniss. Tu veux un peu d'eau ? Oui, maman. Aniss boit de l'eau. L'eau est fraîche. Il se sent plus léger. La lampe est douce. Tes joues sont moins chaudes, maintenant ? Un peu. On reste encore ici ? Oui. La soupe attend, tout doux. Tu as fini de raconter, pour ce soir ? Oui. J'ai raconté. Même si on a ri. Oui. On raconte, quand même. Le manteau mouillé pend au crochet. Il sent encore le parc. Le radiateur fait tic, tout doux. Je l'entends. La louche attend, près de la soupe. On ira à table, dans un moment. Tu as les pieds au sec, maintenant ? Oui, papa. La pluie tapote encore, plus loin. Les chaussures ne gouttent plus. L'abat-jour fait un rond de lumière.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam rentre du parc avec papa. Le soir, la maison est calme. Adam a les joues chaudes. Il pense à des rires. Des enfants ont ri. Adam a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Papa dit : tu peux &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. Raconter, c'est dire ce qui s'est passé. Adam dit : on a ri. J'ai ri aussi. Papa écoute. Maman dit : même si on a ri, on raconte. Même si on a ri, papa est là. Adam raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Papa dit : merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Adam boit de l'eau. Il se sent plus léger. La lampe est douce.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Dans l'entrée, les chaussures gouttent encore. Goutte, goutte, sur le tapis rêche. Une chaussette a glissé, près de la porte. La pluie tapote la vitre. Ça sent la soupe, tout chaud. La lampe du salon a un abat-jour doux. On enlève les chaussures, Aniss. Elles sont lourdes, hein ? Oui, papa. La chaussette, je la prends. Elle est mouillée, elle aussi. Viens près de la lampe. Elle est douce, ce soir. En ce moment, Aniss est à la maison. Il rentre du parc, avec papa. Le soir, la maison est calme. Aniss a les joues chaudes. Il pense à des rires. Des enfants ont ri. Aniss a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Papa écoute. Même si on a ri, on raconte. Même si on a ri, papa t'écoute. Je t'écoute, Aniss. Aniss raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Mon ventre est serré. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Tu as bien fait. Bravo, Aniss. Tu veux un peu d'eau ? Oui, maman. Aniss boit de l'eau. L'eau est fraîche. Il se sent plus léger. La lampe est douce. Tes joues sont moins chaudes, maintenant ? Un peu. On reste encore ici ? Oui. La soupe attend, tout doux. Tu as fini de raconter, pour ce soir ? Oui. J'ai raconté. Même si on a ri. Oui. On raconte, quand même. Le manteau mouillé pend au crochet. Il sent encore le parc. Le radiateur fait tic, tout doux. Je l'entends. La louche attend, près de la soupe. On ira à table, dans un moment. Tu as les pieds au sec, maintenant ? Oui, papa. La pluie tapote encore, plus loin. Les chaussures ne gouttent plus. L'abat-jour fait un rond de lumière.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1364,7 +1364,6 @@
 papa|Même si on a ri, on raconte à papa ou maman.
 maman|Tu as bien fait.
 maman|Bravo, Aniss.
-maman|C'est du bon travail.
 maman|Tu veux un peu d'eau ?
 enfant-m|Oui, maman.
 narrateur|Aniss boit de l'eau.
@@ -1395,7 +1394,6 @@
 narrateur|L'abat-jour fait un rond de lumière.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1425,7 +1423,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Adam a ri un peu. Que fait-il le soir ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a ri un peu. Que fait-il le soir ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1580,7 +1578,6 @@
 narrateur|Que fait-il le soir ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1605,12 +1602,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a su raconter. Même si on a ri, il a parlé à papa et maman. Bravo, Aniss. Tu as fait du bon travail. Tu es venu nous le dire. J'ai raconté. Oui. Même si on a ri.</t>
+          <t>Aniss a su raconter. Même si on a ri, il a parlé à papa et maman. Bravo, Aniss. Tu es venu nous le dire. J'ai raconté. Oui. Même si on a ri.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam a su &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. Même si on a ri, il a parlé à papa et maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a su raconter. Même si on a ri, il a parlé à papa et maman. Bravo, Aniss. Tu es venu nous le dire. J'ai raconté. Oui. Même si on a ri.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1752,14 +1749,12 @@
           <t>narrateur|Aniss a su raconter.
 narrateur|Même si on a ri, il a parlé à papa et maman.
 papa|Bravo, Aniss.
-papa|Tu as fait du bon travail.
 maman|Tu es venu nous le dire.
 enfant-m|J'ai raconté.
 papa|Oui.
 maman|Même si on a ri.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1789,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam met son pyjama. Papa lui tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss met son pyjama. Le tissu est doux, hein ? Oui, papa. Papa lui tient la main. La lampe reste allumée, un peu. Tu as le ventre plus calme ? Oui. La soupe n'est plus trop chaude. La chaussette sèche, près de la porte.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1935,7 +1930,6 @@
 narrateur|La chaussette sèche, près de la porte.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1960,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté. Même si j'ai ri. Bravo. Tu as fait du bon travail. La lampe est encore douce. L'histoire est finie.</t>
+          <t>J'ai raconté. Même si j'ai ri. Bravo. La lampe est encore douce.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté. Même si j'ai ri. Bravo. La lampe est encore douce.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,12 +2097,9 @@
           <t>enfant-m|J'ai raconté.
 enfant-m|Même si j'ai ri.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|La lampe est encore douce.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La lampe est encore douce.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2163,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-01.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-01.xlsx
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -672,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>maison, le soir</t>
         </is>
       </c>
     </row>
@@ -684,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adam, papa, maman</t>
+          <t>Aniss, papa, maman</t>
         </is>
       </c>
     </row>
